--- a/Dados BI 5S.xlsx
+++ b/Dados BI 5S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73DEC63A-EAD8-4DBC-B5E6-04A55ED5D57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846A3DC1-130C-4492-95AF-86B4651696A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Ketlyn</t>
   </si>
   <si>
-    <t>Gabriel </t>
-  </si>
-  <si>
     <t>Gabriel</t>
   </si>
 </sst>
@@ -187,11 +184,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -48973,7 +48969,7 @@
       <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -48994,7 +48990,7 @@
       <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49015,7 +49011,7 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="3" t="str">
+      <c r="G4" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49036,7 +49032,7 @@
       <c r="F5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="3" t="str">
+      <c r="G5" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49057,7 +49053,7 @@
       <c r="F6" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="3" t="str">
+      <c r="G6" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49078,7 +49074,7 @@
       <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="3" t="str">
+      <c r="G7" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49099,7 +49095,7 @@
       <c r="F8" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3" t="str">
+      <c r="G8" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49120,7 +49116,7 @@
       <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="3" t="str">
+      <c r="G9" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49141,7 +49137,7 @@
       <c r="F10" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="3" t="str">
+      <c r="G10" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49162,7 +49158,7 @@
       <c r="F11" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="3" t="str">
+      <c r="G11" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49183,7 +49179,7 @@
       <c r="F12" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="3" t="str">
+      <c r="G12" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49207,7 +49203,7 @@
       <c r="F13" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="3" t="str">
+      <c r="G13" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49231,7 +49227,7 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3" t="str">
+      <c r="G14" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49255,7 +49251,7 @@
       <c r="F15" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="3" t="str">
+      <c r="G15" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49279,7 +49275,7 @@
       <c r="F16" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="3" t="str">
+      <c r="G16" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49303,7 +49299,7 @@
       <c r="F17" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="3" t="str">
+      <c r="G17" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49327,7 +49323,7 @@
       <c r="F18" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="3" t="str">
+      <c r="G18" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49351,7 +49347,7 @@
       <c r="F19" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="3" t="str">
+      <c r="G19" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49375,7 +49371,7 @@
       <c r="F20" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="3" t="str">
+      <c r="G20" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/04</v>
       </c>
@@ -49399,7 +49395,7 @@
       <c r="F21" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="3" t="str">
+      <c r="G21" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49423,7 +49419,7 @@
       <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="3" t="str">
+      <c r="G22" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49447,7 +49443,7 @@
       <c r="F23" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="3" t="str">
+      <c r="G23" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49471,7 +49467,7 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="3" t="str">
+      <c r="G24" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49495,7 +49491,7 @@
       <c r="F25" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="3" t="str">
+      <c r="G25" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49519,7 +49515,7 @@
       <c r="F26" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="3" t="str">
+      <c r="G26" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49543,7 +49539,7 @@
       <c r="F27" t="s">
         <v>9</v>
       </c>
-      <c r="G27" s="3" t="str">
+      <c r="G27" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49567,7 +49563,7 @@
       <c r="F28" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="3" t="str">
+      <c r="G28" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49591,7 +49587,7 @@
       <c r="F29" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3" t="str">
+      <c r="G29" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49615,7 +49611,7 @@
       <c r="F30" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="3" t="str">
+      <c r="G30" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49639,7 +49635,7 @@
       <c r="F31" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="3" t="str">
+      <c r="G31" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49663,7 +49659,7 @@
       <c r="F32" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3" t="str">
+      <c r="G32" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49687,7 +49683,7 @@
       <c r="F33" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="3" t="str">
+      <c r="G33" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49711,7 +49707,7 @@
       <c r="F34" t="s">
         <v>14</v>
       </c>
-      <c r="G34" s="3" t="str">
+      <c r="G34" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49735,7 +49731,7 @@
       <c r="F35" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="3" t="str">
+      <c r="G35" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49759,7 +49755,7 @@
       <c r="F36" t="s">
         <v>8</v>
       </c>
-      <c r="G36" s="3" t="str">
+      <c r="G36" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49783,7 +49779,7 @@
       <c r="F37" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="3" t="str">
+      <c r="G37" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49807,7 +49803,7 @@
       <c r="F38" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="3" t="str">
+      <c r="G38" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49831,7 +49827,7 @@
       <c r="F39" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="3" t="str">
+      <c r="G39" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49855,7 +49851,7 @@
       <c r="F40" t="s">
         <v>8</v>
       </c>
-      <c r="G40" s="3" t="str">
+      <c r="G40" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49879,7 +49875,7 @@
       <c r="F41" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="3" t="str">
+      <c r="G41" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/05</v>
       </c>
@@ -49903,7 +49899,7 @@
       <c r="F42" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="3" t="str">
+      <c r="G42" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -49927,7 +49923,7 @@
       <c r="F43" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="3" t="str">
+      <c r="G43" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -49951,7 +49947,7 @@
       <c r="F44" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3" t="str">
+      <c r="G44" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -49975,7 +49971,7 @@
       <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="3" t="str">
+      <c r="G45" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -49999,7 +49995,7 @@
       <c r="F46" t="s">
         <v>9</v>
       </c>
-      <c r="G46" s="3" t="str">
+      <c r="G46" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50023,7 +50019,7 @@
       <c r="F47" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3" t="str">
+      <c r="G47" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50047,7 +50043,7 @@
       <c r="F48" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="3" t="str">
+      <c r="G48" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50071,7 +50067,7 @@
       <c r="F49" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="3" t="str">
+      <c r="G49" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50095,7 +50091,7 @@
       <c r="F50" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="3" t="str">
+      <c r="G50" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50119,7 +50115,7 @@
       <c r="F51" t="s">
         <v>8</v>
       </c>
-      <c r="G51" s="3" t="str">
+      <c r="G51" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50143,7 +50139,7 @@
       <c r="F52" t="s">
         <v>9</v>
       </c>
-      <c r="G52" s="3" t="str">
+      <c r="G52" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50167,7 +50163,7 @@
       <c r="F53" t="s">
         <v>13</v>
       </c>
-      <c r="G53" s="3" t="str">
+      <c r="G53" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50191,7 +50187,7 @@
       <c r="F54" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="3" t="str">
+      <c r="G54" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50215,7 +50211,7 @@
       <c r="F55" t="s">
         <v>8</v>
       </c>
-      <c r="G55" s="3" t="str">
+      <c r="G55" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50239,7 +50235,7 @@
       <c r="F56" t="s">
         <v>9</v>
       </c>
-      <c r="G56" s="3" t="str">
+      <c r="G56" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50263,7 +50259,7 @@
       <c r="F57" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="3" t="str">
+      <c r="G57" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50287,7 +50283,7 @@
       <c r="F58" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="3" t="str">
+      <c r="G58" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50311,7 +50307,7 @@
       <c r="F59" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3" t="str">
+      <c r="G59" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50335,7 +50331,7 @@
       <c r="F60" t="s">
         <v>9</v>
       </c>
-      <c r="G60" s="3" t="str">
+      <c r="G60" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50359,7 +50355,7 @@
       <c r="F61" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="3" t="str">
+      <c r="G61" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/06</v>
       </c>
@@ -50383,7 +50379,7 @@
       <c r="F62" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3" t="str">
+      <c r="G62" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50407,7 +50403,7 @@
       <c r="F63" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="3" t="str">
+      <c r="G63" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50431,7 +50427,7 @@
       <c r="F64" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="3" t="str">
+      <c r="G64" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50455,7 +50451,7 @@
       <c r="F65" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="3" t="str">
+      <c r="G65" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50479,7 +50475,7 @@
       <c r="F66" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="3" t="str">
+      <c r="G66" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50503,7 +50499,7 @@
       <c r="F67" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="3" t="str">
+      <c r="G67" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50527,7 +50523,7 @@
       <c r="F68" t="s">
         <v>9</v>
       </c>
-      <c r="G68" s="3" t="str">
+      <c r="G68" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50551,7 +50547,7 @@
       <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="3" t="str">
+      <c r="G69" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50575,7 +50571,7 @@
       <c r="F70" t="s">
         <v>8</v>
       </c>
-      <c r="G70" s="3" t="str">
+      <c r="G70" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50599,7 +50595,7 @@
       <c r="F71" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="3" t="str">
+      <c r="G71" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50623,7 +50619,7 @@
       <c r="F72" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="3" t="str">
+      <c r="G72" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50647,7 +50643,7 @@
       <c r="F73" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="3" t="str">
+      <c r="G73" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50671,7 +50667,7 @@
       <c r="F74" t="s">
         <v>11</v>
       </c>
-      <c r="G74" s="3" t="str">
+      <c r="G74" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50695,7 +50691,7 @@
       <c r="F75" t="s">
         <v>9</v>
       </c>
-      <c r="G75" s="3" t="str">
+      <c r="G75" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50719,7 +50715,7 @@
       <c r="F76" t="s">
         <v>9</v>
       </c>
-      <c r="G76" s="3" t="str">
+      <c r="G76" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50743,7 +50739,7 @@
       <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="3" t="str">
+      <c r="G77" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50767,7 +50763,7 @@
       <c r="F78" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="3" t="str">
+      <c r="G78" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50791,7 +50787,7 @@
       <c r="F79" t="s">
         <v>9</v>
       </c>
-      <c r="G79" s="3" t="str">
+      <c r="G79" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50815,7 +50811,7 @@
       <c r="F80" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="3" t="str">
+      <c r="G80" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50839,7 +50835,7 @@
       <c r="F81" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="3" t="str">
+      <c r="G81" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50863,7 +50859,7 @@
       <c r="F82" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="3" t="str">
+      <c r="G82" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50887,7 +50883,7 @@
       <c r="F83" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3" t="str">
+      <c r="G83" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50911,7 +50907,7 @@
       <c r="F84" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="3" t="str">
+      <c r="G84" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50935,7 +50931,7 @@
       <c r="F85" t="s">
         <v>11</v>
       </c>
-      <c r="G85" s="3" t="str">
+      <c r="G85" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50959,7 +50955,7 @@
       <c r="F86" t="s">
         <v>8</v>
       </c>
-      <c r="G86" s="3" t="str">
+      <c r="G86" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -50983,7 +50979,7 @@
       <c r="F87" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="3" t="str">
+      <c r="G87" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51007,7 +51003,7 @@
       <c r="F88" t="s">
         <v>14</v>
       </c>
-      <c r="G88" s="3" t="str">
+      <c r="G88" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51031,7 +51027,7 @@
       <c r="F89" t="s">
         <v>13</v>
       </c>
-      <c r="G89" s="3" t="str">
+      <c r="G89" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51055,7 +51051,7 @@
       <c r="F90" t="s">
         <v>9</v>
       </c>
-      <c r="G90" s="3" t="str">
+      <c r="G90" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51079,7 +51075,7 @@
       <c r="F91" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3" t="str">
+      <c r="G91" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51103,7 +51099,7 @@
       <c r="F92" t="s">
         <v>11</v>
       </c>
-      <c r="G92" s="3" t="str">
+      <c r="G92" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51127,7 +51123,7 @@
       <c r="F93" t="s">
         <v>14</v>
       </c>
-      <c r="G93" s="3" t="str">
+      <c r="G93" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51151,7 +51147,7 @@
       <c r="F94" t="s">
         <v>14</v>
       </c>
-      <c r="G94" s="3" t="str">
+      <c r="G94" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51175,7 +51171,7 @@
       <c r="F95" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="3" t="str">
+      <c r="G95" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51199,7 +51195,7 @@
       <c r="F96" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3" t="str">
+      <c r="G96" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51223,7 +51219,7 @@
       <c r="F97" t="s">
         <v>13</v>
       </c>
-      <c r="G97" s="3" t="str">
+      <c r="G97" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51247,7 +51243,7 @@
       <c r="F98" t="s">
         <v>11</v>
       </c>
-      <c r="G98" s="3" t="str">
+      <c r="G98" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51271,7 +51267,7 @@
       <c r="F99" t="s">
         <v>10</v>
       </c>
-      <c r="G99" s="3" t="str">
+      <c r="G99" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51295,7 +51291,7 @@
       <c r="F100" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="3" t="str">
+      <c r="G100" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51319,7 +51315,7 @@
       <c r="F101" t="s">
         <v>14</v>
       </c>
-      <c r="G101" s="3" t="str">
+      <c r="G101" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51343,7 +51339,7 @@
       <c r="F102" t="s">
         <v>13</v>
       </c>
-      <c r="G102" s="3" t="str">
+      <c r="G102" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51367,7 +51363,7 @@
       <c r="F103" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="3" t="str">
+      <c r="G103" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51391,7 +51387,7 @@
       <c r="F104" t="s">
         <v>10</v>
       </c>
-      <c r="G104" s="3" t="str">
+      <c r="G104" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51415,7 +51411,7 @@
       <c r="F105" t="s">
         <v>11</v>
       </c>
-      <c r="G105" s="3" t="str">
+      <c r="G105" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51439,7 +51435,7 @@
       <c r="F106" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="3" t="str">
+      <c r="G106" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51463,7 +51459,7 @@
       <c r="F107" t="s">
         <v>8</v>
       </c>
-      <c r="G107" s="3" t="str">
+      <c r="G107" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51487,7 +51483,7 @@
       <c r="F108" t="s">
         <v>11</v>
       </c>
-      <c r="G108" s="3" t="str">
+      <c r="G108" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51511,7 +51507,7 @@
       <c r="F109" t="s">
         <v>10</v>
       </c>
-      <c r="G109" s="3" t="str">
+      <c r="G109" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51535,7 +51531,7 @@
       <c r="F110" t="s">
         <v>10</v>
       </c>
-      <c r="G110" s="3" t="str">
+      <c r="G110" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51559,7 +51555,7 @@
       <c r="F111" t="s">
         <v>11</v>
       </c>
-      <c r="G111" s="3" t="str">
+      <c r="G111" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51583,7 +51579,7 @@
       <c r="F112" t="s">
         <v>8</v>
       </c>
-      <c r="G112" s="3" t="str">
+      <c r="G112" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51607,7 +51603,7 @@
       <c r="F113" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="3" t="str">
+      <c r="G113" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51631,7 +51627,7 @@
       <c r="F114" t="s">
         <v>9</v>
       </c>
-      <c r="G114" s="3" t="str">
+      <c r="G114" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51655,7 +51651,7 @@
       <c r="F115" t="s">
         <v>10</v>
       </c>
-      <c r="G115" s="3" t="str">
+      <c r="G115" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51679,7 +51675,7 @@
       <c r="F116" t="s">
         <v>11</v>
       </c>
-      <c r="G116" s="3" t="str">
+      <c r="G116" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/07</v>
       </c>
@@ -51703,7 +51699,7 @@
       <c r="F117" t="s">
         <v>13</v>
       </c>
-      <c r="G117" s="3" t="str">
+      <c r="G117" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51727,7 +51723,7 @@
       <c r="F118" t="s">
         <v>8</v>
       </c>
-      <c r="G118" s="3" t="str">
+      <c r="G118" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51751,7 +51747,7 @@
       <c r="F119" t="s">
         <v>14</v>
       </c>
-      <c r="G119" s="3" t="str">
+      <c r="G119" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51775,7 +51771,7 @@
       <c r="F120" t="s">
         <v>10</v>
       </c>
-      <c r="G120" s="3" t="str">
+      <c r="G120" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51799,7 +51795,7 @@
       <c r="F121" t="s">
         <v>11</v>
       </c>
-      <c r="G121" s="3" t="str">
+      <c r="G121" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51823,7 +51819,7 @@
       <c r="F122" t="s">
         <v>8</v>
       </c>
-      <c r="G122" s="3" t="str">
+      <c r="G122" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51847,7 +51843,7 @@
       <c r="F123" t="s">
         <v>13</v>
       </c>
-      <c r="G123" s="3" t="str">
+      <c r="G123" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51871,7 +51867,7 @@
       <c r="F124" t="s">
         <v>8</v>
       </c>
-      <c r="G124" s="3" t="str">
+      <c r="G124" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51895,7 +51891,7 @@
       <c r="F125" t="s">
         <v>11</v>
       </c>
-      <c r="G125" s="3" t="str">
+      <c r="G125" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51919,7 +51915,7 @@
       <c r="F126" t="s">
         <v>10</v>
       </c>
-      <c r="G126" s="3" t="str">
+      <c r="G126" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51943,7 +51939,7 @@
       <c r="F127" t="s">
         <v>13</v>
       </c>
-      <c r="G127" s="3" t="str">
+      <c r="G127" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51967,7 +51963,7 @@
       <c r="F128" t="s">
         <v>8</v>
       </c>
-      <c r="G128" s="3" t="str">
+      <c r="G128" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -51991,7 +51987,7 @@
       <c r="F129" t="s">
         <v>8</v>
       </c>
-      <c r="G129" s="3" t="str">
+      <c r="G129" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52015,7 +52011,7 @@
       <c r="F130" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="3" t="str">
+      <c r="G130" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52039,7 +52035,7 @@
       <c r="F131" t="s">
         <v>11</v>
       </c>
-      <c r="G131" s="3" t="str">
+      <c r="G131" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52063,7 +52059,7 @@
       <c r="F132" t="s">
         <v>8</v>
       </c>
-      <c r="G132" s="3" t="str">
+      <c r="G132" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52087,7 +52083,7 @@
       <c r="F133" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="3" t="str">
+      <c r="G133" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52111,7 +52107,7 @@
       <c r="F134" t="s">
         <v>14</v>
       </c>
-      <c r="G134" s="3" t="str">
+      <c r="G134" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52135,7 +52131,7 @@
       <c r="F135" t="s">
         <v>9</v>
       </c>
-      <c r="G135" s="3" t="str">
+      <c r="G135" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52159,7 +52155,7 @@
       <c r="F136" t="s">
         <v>8</v>
       </c>
-      <c r="G136" s="3" t="str">
+      <c r="G136" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52183,7 +52179,7 @@
       <c r="F137" t="s">
         <v>13</v>
       </c>
-      <c r="G137" s="3" t="str">
+      <c r="G137" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52207,7 +52203,7 @@
       <c r="F138" t="s">
         <v>8</v>
       </c>
-      <c r="G138" s="3" t="str">
+      <c r="G138" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52231,7 +52227,7 @@
       <c r="F139" t="s">
         <v>9</v>
       </c>
-      <c r="G139" s="3" t="str">
+      <c r="G139" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52255,7 +52251,7 @@
       <c r="F140" t="s">
         <v>9</v>
       </c>
-      <c r="G140" s="3" t="str">
+      <c r="G140" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52279,7 +52275,7 @@
       <c r="F141" t="s">
         <v>14</v>
       </c>
-      <c r="G141" s="3" t="str">
+      <c r="G141" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52303,7 +52299,7 @@
       <c r="F142" t="s">
         <v>8</v>
       </c>
-      <c r="G142" s="3" t="str">
+      <c r="G142" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52327,7 +52323,7 @@
       <c r="F143" t="s">
         <v>8</v>
       </c>
-      <c r="G143" s="3" t="str">
+      <c r="G143" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52351,7 +52347,7 @@
       <c r="F144" t="s">
         <v>10</v>
       </c>
-      <c r="G144" s="3" t="str">
+      <c r="G144" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52375,7 +52371,7 @@
       <c r="F145" t="s">
         <v>13</v>
       </c>
-      <c r="G145" s="3" t="str">
+      <c r="G145" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52399,7 +52395,7 @@
       <c r="F146" t="s">
         <v>9</v>
       </c>
-      <c r="G146" s="3" t="str">
+      <c r="G146" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52423,7 +52419,7 @@
       <c r="F147" t="s">
         <v>13</v>
       </c>
-      <c r="G147" s="3" t="str">
+      <c r="G147" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52447,7 +52443,7 @@
       <c r="F148" t="s">
         <v>9</v>
       </c>
-      <c r="G148" s="3" t="str">
+      <c r="G148" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52471,7 +52467,7 @@
       <c r="F149" t="s">
         <v>9</v>
       </c>
-      <c r="G149" s="3" t="str">
+      <c r="G149" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52495,7 +52491,7 @@
       <c r="F150" t="s">
         <v>8</v>
       </c>
-      <c r="G150" s="3" t="str">
+      <c r="G150" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52519,7 +52515,7 @@
       <c r="F151" t="s">
         <v>14</v>
       </c>
-      <c r="G151" s="3" t="str">
+      <c r="G151" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52543,7 +52539,7 @@
       <c r="F152" t="s">
         <v>10</v>
       </c>
-      <c r="G152" s="3" t="str">
+      <c r="G152" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52567,7 +52563,7 @@
       <c r="F153" t="s">
         <v>8</v>
       </c>
-      <c r="G153" s="3" t="str">
+      <c r="G153" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52591,7 +52587,7 @@
       <c r="F154" t="s">
         <v>12</v>
       </c>
-      <c r="G154" s="3" t="str">
+      <c r="G154" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52615,7 +52611,7 @@
       <c r="F155" t="s">
         <v>9</v>
       </c>
-      <c r="G155" s="3" t="str">
+      <c r="G155" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52639,7 +52635,7 @@
       <c r="F156" t="s">
         <v>13</v>
       </c>
-      <c r="G156" s="3" t="str">
+      <c r="G156" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52663,7 +52659,7 @@
       <c r="F157" t="s">
         <v>8</v>
       </c>
-      <c r="G157" s="3" t="str">
+      <c r="G157" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52687,7 +52683,7 @@
       <c r="F158" t="s">
         <v>8</v>
       </c>
-      <c r="G158" s="3" t="str">
+      <c r="G158" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52711,7 +52707,7 @@
       <c r="F159" t="s">
         <v>13</v>
       </c>
-      <c r="G159" s="3" t="str">
+      <c r="G159" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52735,7 +52731,7 @@
       <c r="F160" t="s">
         <v>9</v>
       </c>
-      <c r="G160" s="3" t="str">
+      <c r="G160" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52759,7 +52755,7 @@
       <c r="F161" t="s">
         <v>9</v>
       </c>
-      <c r="G161" s="3" t="str">
+      <c r="G161" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52783,7 +52779,7 @@
       <c r="F162" t="s">
         <v>14</v>
       </c>
-      <c r="G162" s="3" t="str">
+      <c r="G162" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52807,7 +52803,7 @@
       <c r="F163" t="s">
         <v>14</v>
       </c>
-      <c r="G163" s="3" t="str">
+      <c r="G163" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52831,7 +52827,7 @@
       <c r="F164" t="s">
         <v>8</v>
       </c>
-      <c r="G164" s="3" t="str">
+      <c r="G164" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52855,7 +52851,7 @@
       <c r="F165" t="s">
         <v>9</v>
       </c>
-      <c r="G165" s="3" t="str">
+      <c r="G165" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52879,7 +52875,7 @@
       <c r="F166" t="s">
         <v>8</v>
       </c>
-      <c r="G166" s="3" t="str">
+      <c r="G166" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52903,7 +52899,7 @@
       <c r="F167" t="s">
         <v>12</v>
       </c>
-      <c r="G167" s="3" t="str">
+      <c r="G167" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52927,7 +52923,7 @@
       <c r="F168" t="s">
         <v>13</v>
       </c>
-      <c r="G168" s="3" t="str">
+      <c r="G168" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52951,7 +52947,7 @@
       <c r="F169" t="s">
         <v>9</v>
       </c>
-      <c r="G169" s="3" t="str">
+      <c r="G169" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52975,7 +52971,7 @@
       <c r="F170" t="s">
         <v>14</v>
       </c>
-      <c r="G170" s="3" t="str">
+      <c r="G170" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -52999,7 +52995,7 @@
       <c r="F171" t="s">
         <v>9</v>
       </c>
-      <c r="G171" s="3" t="str">
+      <c r="G171" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -53023,7 +53019,7 @@
       <c r="F172" t="s">
         <v>13</v>
       </c>
-      <c r="G172" s="3" t="str">
+      <c r="G172" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -53047,7 +53043,7 @@
       <c r="F173" t="s">
         <v>9</v>
       </c>
-      <c r="G173" s="3" t="str">
+      <c r="G173" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -53071,7 +53067,7 @@
       <c r="F174" t="s">
         <v>8</v>
       </c>
-      <c r="G174" s="3" t="str">
+      <c r="G174" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/08</v>
       </c>
@@ -53095,7 +53091,7 @@
       <c r="F175" t="s">
         <v>11</v>
       </c>
-      <c r="G175" s="3" t="str">
+      <c r="G175" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53119,7 +53115,7 @@
       <c r="F176" t="s">
         <v>8</v>
       </c>
-      <c r="G176" s="3" t="str">
+      <c r="G176" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53143,7 +53139,7 @@
       <c r="F177" t="s">
         <v>14</v>
       </c>
-      <c r="G177" s="3" t="str">
+      <c r="G177" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53167,7 +53163,7 @@
       <c r="F178" t="s">
         <v>8</v>
       </c>
-      <c r="G178" s="3" t="str">
+      <c r="G178" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53191,7 +53187,7 @@
       <c r="F179" t="s">
         <v>13</v>
       </c>
-      <c r="G179" s="3" t="str">
+      <c r="G179" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53215,7 +53211,7 @@
       <c r="F180" t="s">
         <v>9</v>
       </c>
-      <c r="G180" s="3" t="str">
+      <c r="G180" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53239,7 +53235,7 @@
       <c r="F181" t="s">
         <v>8</v>
       </c>
-      <c r="G181" s="3" t="str">
+      <c r="G181" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53263,7 +53259,7 @@
       <c r="F182" t="s">
         <v>8</v>
       </c>
-      <c r="G182" s="3" t="str">
+      <c r="G182" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53287,7 +53283,7 @@
       <c r="F183" t="s">
         <v>13</v>
       </c>
-      <c r="G183" s="3" t="str">
+      <c r="G183" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53311,7 +53307,7 @@
       <c r="F184" t="s">
         <v>10</v>
       </c>
-      <c r="G184" s="3" t="str">
+      <c r="G184" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53335,7 +53331,7 @@
       <c r="F185" t="s">
         <v>12</v>
       </c>
-      <c r="G185" s="3" t="str">
+      <c r="G185" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53359,7 +53355,7 @@
       <c r="F186" t="s">
         <v>8</v>
       </c>
-      <c r="G186" s="3" t="str">
+      <c r="G186" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53383,7 +53379,7 @@
       <c r="F187" t="s">
         <v>13</v>
       </c>
-      <c r="G187" s="3" t="str">
+      <c r="G187" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53407,7 +53403,7 @@
       <c r="F188" t="s">
         <v>8</v>
       </c>
-      <c r="G188" s="3" t="str">
+      <c r="G188" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53431,7 +53427,7 @@
       <c r="F189" t="s">
         <v>8</v>
       </c>
-      <c r="G189" s="3" t="str">
+      <c r="G189" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53455,7 +53451,7 @@
       <c r="F190" t="s">
         <v>12</v>
       </c>
-      <c r="G190" s="3" t="str">
+      <c r="G190" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53479,7 +53475,7 @@
       <c r="F191" t="s">
         <v>14</v>
       </c>
-      <c r="G191" s="3" t="str">
+      <c r="G191" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53503,7 +53499,7 @@
       <c r="F192" t="s">
         <v>8</v>
       </c>
-      <c r="G192" s="3" t="str">
+      <c r="G192" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53527,7 +53523,7 @@
       <c r="F193" t="s">
         <v>8</v>
       </c>
-      <c r="G193" s="3" t="str">
+      <c r="G193" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53551,7 +53547,7 @@
       <c r="F194" t="s">
         <v>8</v>
       </c>
-      <c r="G194" s="3" t="str">
+      <c r="G194" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53575,7 +53571,7 @@
       <c r="F195" t="s">
         <v>12</v>
       </c>
-      <c r="G195" s="3" t="str">
+      <c r="G195" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53599,7 +53595,7 @@
       <c r="F196" t="s">
         <v>11</v>
       </c>
-      <c r="G196" s="3" t="str">
+      <c r="G196" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53623,7 +53619,7 @@
       <c r="F197" t="s">
         <v>8</v>
       </c>
-      <c r="G197" s="3" t="str">
+      <c r="G197" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53647,7 +53643,7 @@
       <c r="F198" t="s">
         <v>10</v>
       </c>
-      <c r="G198" s="3" t="str">
+      <c r="G198" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53671,7 +53667,7 @@
       <c r="F199" t="s">
         <v>14</v>
       </c>
-      <c r="G199" s="3" t="str">
+      <c r="G199" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53695,7 +53691,7 @@
       <c r="F200" t="s">
         <v>9</v>
       </c>
-      <c r="G200" s="3" t="str">
+      <c r="G200" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53719,7 +53715,7 @@
       <c r="F201" t="s">
         <v>10</v>
       </c>
-      <c r="G201" s="3" t="str">
+      <c r="G201" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53743,7 +53739,7 @@
       <c r="F202" t="s">
         <v>12</v>
       </c>
-      <c r="G202" s="3" t="str">
+      <c r="G202" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53767,7 +53763,7 @@
       <c r="F203" t="s">
         <v>13</v>
       </c>
-      <c r="G203" s="3" t="str">
+      <c r="G203" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53791,7 +53787,7 @@
       <c r="F204" t="s">
         <v>8</v>
       </c>
-      <c r="G204" s="3" t="str">
+      <c r="G204" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53815,7 +53811,7 @@
       <c r="F205" t="s">
         <v>8</v>
       </c>
-      <c r="G205" s="3" t="str">
+      <c r="G205" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53839,7 +53835,7 @@
       <c r="F206" t="s">
         <v>8</v>
       </c>
-      <c r="G206" s="3" t="str">
+      <c r="G206" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53863,7 +53859,7 @@
       <c r="F207" t="s">
         <v>8</v>
       </c>
-      <c r="G207" s="3" t="str">
+      <c r="G207" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53887,7 +53883,7 @@
       <c r="F208" t="s">
         <v>14</v>
       </c>
-      <c r="G208" s="3" t="str">
+      <c r="G208" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53911,7 +53907,7 @@
       <c r="F209" t="s">
         <v>8</v>
       </c>
-      <c r="G209" s="3" t="str">
+      <c r="G209" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53935,7 +53931,7 @@
       <c r="F210" t="s">
         <v>9</v>
       </c>
-      <c r="G210" s="3" t="str">
+      <c r="G210" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53959,7 +53955,7 @@
       <c r="F211" t="s">
         <v>12</v>
       </c>
-      <c r="G211" s="3" t="str">
+      <c r="G211" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -53983,7 +53979,7 @@
       <c r="F212" t="s">
         <v>8</v>
       </c>
-      <c r="G212" s="3" t="str">
+      <c r="G212" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54007,7 +54003,7 @@
       <c r="F213" t="s">
         <v>13</v>
       </c>
-      <c r="G213" s="3" t="str">
+      <c r="G213" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54031,7 +54027,7 @@
       <c r="F214" t="s">
         <v>8</v>
       </c>
-      <c r="G214" s="3" t="str">
+      <c r="G214" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54055,7 +54051,7 @@
       <c r="F215" t="s">
         <v>13</v>
       </c>
-      <c r="G215" s="3" t="str">
+      <c r="G215" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54079,7 +54075,7 @@
       <c r="F216" t="s">
         <v>8</v>
       </c>
-      <c r="G216" s="3" t="str">
+      <c r="G216" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54103,7 +54099,7 @@
       <c r="F217" t="s">
         <v>8</v>
       </c>
-      <c r="G217" s="3" t="str">
+      <c r="G217" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54127,7 +54123,7 @@
       <c r="F218" t="s">
         <v>13</v>
       </c>
-      <c r="G218" s="3" t="str">
+      <c r="G218" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/09</v>
       </c>
@@ -54151,7 +54147,7 @@
       <c r="F219" t="s">
         <v>8</v>
       </c>
-      <c r="G219" s="3" t="str">
+      <c r="G219" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54175,7 +54171,7 @@
       <c r="F220" t="s">
         <v>8</v>
       </c>
-      <c r="G220" s="3" t="str">
+      <c r="G220" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54199,7 +54195,7 @@
       <c r="F221" t="s">
         <v>8</v>
       </c>
-      <c r="G221" s="3" t="str">
+      <c r="G221" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54223,7 +54219,7 @@
       <c r="F222" t="s">
         <v>10</v>
       </c>
-      <c r="G222" s="3" t="str">
+      <c r="G222" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54247,7 +54243,7 @@
       <c r="F223" t="s">
         <v>8</v>
       </c>
-      <c r="G223" s="3" t="str">
+      <c r="G223" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54271,7 +54267,7 @@
       <c r="F224" t="s">
         <v>13</v>
       </c>
-      <c r="G224" s="3" t="str">
+      <c r="G224" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54295,7 +54291,7 @@
       <c r="F225" t="s">
         <v>8</v>
       </c>
-      <c r="G225" s="3" t="str">
+      <c r="G225" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54319,7 +54315,7 @@
       <c r="F226" t="s">
         <v>13</v>
       </c>
-      <c r="G226" s="3" t="str">
+      <c r="G226" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54343,7 +54339,7 @@
       <c r="F227" t="s">
         <v>8</v>
       </c>
-      <c r="G227" s="3" t="str">
+      <c r="G227" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54367,7 +54363,7 @@
       <c r="F228" t="s">
         <v>8</v>
       </c>
-      <c r="G228" s="3" t="str">
+      <c r="G228" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54391,7 +54387,7 @@
       <c r="F229" t="s">
         <v>9</v>
       </c>
-      <c r="G229" s="3" t="str">
+      <c r="G229" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54415,7 +54411,7 @@
       <c r="F230" t="s">
         <v>11</v>
       </c>
-      <c r="G230" s="3" t="str">
+      <c r="G230" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54439,7 +54435,7 @@
       <c r="F231" t="s">
         <v>8</v>
       </c>
-      <c r="G231" s="3" t="str">
+      <c r="G231" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54463,7 +54459,7 @@
       <c r="F232" t="s">
         <v>10</v>
       </c>
-      <c r="G232" s="3" t="str">
+      <c r="G232" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54487,7 +54483,7 @@
       <c r="F233" t="s">
         <v>8</v>
       </c>
-      <c r="G233" s="3" t="str">
+      <c r="G233" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54511,7 +54507,7 @@
       <c r="F234" t="s">
         <v>9</v>
       </c>
-      <c r="G234" s="3" t="str">
+      <c r="G234" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54535,7 +54531,7 @@
       <c r="F235" t="s">
         <v>14</v>
       </c>
-      <c r="G235" s="3" t="str">
+      <c r="G235" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54559,7 +54555,7 @@
       <c r="F236" t="s">
         <v>10</v>
       </c>
-      <c r="G236" s="3" t="str">
+      <c r="G236" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54583,7 +54579,7 @@
       <c r="F237" t="s">
         <v>12</v>
       </c>
-      <c r="G237" s="3" t="str">
+      <c r="G237" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54607,7 +54603,7 @@
       <c r="F238" t="s">
         <v>11</v>
       </c>
-      <c r="G238" s="3" t="str">
+      <c r="G238" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54631,7 +54627,7 @@
       <c r="F239" t="s">
         <v>9</v>
       </c>
-      <c r="G239" s="3" t="str">
+      <c r="G239" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54655,7 +54651,7 @@
       <c r="F240" t="s">
         <v>8</v>
       </c>
-      <c r="G240" s="3" t="str">
+      <c r="G240" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54679,7 +54675,7 @@
       <c r="F241" t="s">
         <v>10</v>
       </c>
-      <c r="G241" s="3" t="str">
+      <c r="G241" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54703,7 +54699,7 @@
       <c r="F242" t="s">
         <v>13</v>
       </c>
-      <c r="G242" s="3" t="str">
+      <c r="G242" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54727,7 +54723,7 @@
       <c r="F243" t="s">
         <v>8</v>
       </c>
-      <c r="G243" s="3" t="str">
+      <c r="G243" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54751,7 +54747,7 @@
       <c r="F244" t="s">
         <v>9</v>
       </c>
-      <c r="G244" s="3" t="str">
+      <c r="G244" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54775,7 +54771,7 @@
       <c r="F245" t="s">
         <v>8</v>
       </c>
-      <c r="G245" s="3" t="str">
+      <c r="G245" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54799,7 +54795,7 @@
       <c r="F246" t="s">
         <v>13</v>
       </c>
-      <c r="G246" s="3" t="str">
+      <c r="G246" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54823,7 +54819,7 @@
       <c r="F247" t="s">
         <v>12</v>
       </c>
-      <c r="G247" s="3" t="str">
+      <c r="G247" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54847,7 +54843,7 @@
       <c r="F248" t="s">
         <v>8</v>
       </c>
-      <c r="G248" s="3" t="str">
+      <c r="G248" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54871,7 +54867,7 @@
       <c r="F249" t="s">
         <v>8</v>
       </c>
-      <c r="G249" s="3" t="str">
+      <c r="G249" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54895,7 +54891,7 @@
       <c r="F250" t="s">
         <v>13</v>
       </c>
-      <c r="G250" s="3" t="str">
+      <c r="G250" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54919,7 +54915,7 @@
       <c r="F251" t="s">
         <v>8</v>
       </c>
-      <c r="G251" s="3" t="str">
+      <c r="G251" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54943,7 +54939,7 @@
       <c r="F252" t="s">
         <v>8</v>
       </c>
-      <c r="G252" s="3" t="str">
+      <c r="G252" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54967,7 +54963,7 @@
       <c r="F253" t="s">
         <v>13</v>
       </c>
-      <c r="G253" s="3" t="str">
+      <c r="G253" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -54991,7 +54987,7 @@
       <c r="F254" t="s">
         <v>8</v>
       </c>
-      <c r="G254" s="3" t="str">
+      <c r="G254" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55015,7 +55011,7 @@
       <c r="F255" t="s">
         <v>10</v>
       </c>
-      <c r="G255" s="3" t="str">
+      <c r="G255" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55039,7 +55035,7 @@
       <c r="F256" t="s">
         <v>9</v>
       </c>
-      <c r="G256" s="3" t="str">
+      <c r="G256" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55063,7 +55059,7 @@
       <c r="F257" t="s">
         <v>13</v>
       </c>
-      <c r="G257" s="3" t="str">
+      <c r="G257" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55087,7 +55083,7 @@
       <c r="F258" t="s">
         <v>12</v>
       </c>
-      <c r="G258" s="3" t="str">
+      <c r="G258" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55111,7 +55107,7 @@
       <c r="F259" t="s">
         <v>10</v>
       </c>
-      <c r="G259" s="3" t="str">
+      <c r="G259" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55135,7 +55131,7 @@
       <c r="F260" t="s">
         <v>8</v>
       </c>
-      <c r="G260" s="3" t="str">
+      <c r="G260" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55159,7 +55155,7 @@
       <c r="F261" t="s">
         <v>13</v>
       </c>
-      <c r="G261" s="3" t="str">
+      <c r="G261" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55183,7 +55179,7 @@
       <c r="F262" t="s">
         <v>9</v>
       </c>
-      <c r="G262" s="3" t="str">
+      <c r="G262" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55207,7 +55203,7 @@
       <c r="F263" t="s">
         <v>13</v>
       </c>
-      <c r="G263" s="3" t="str">
+      <c r="G263" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55231,7 +55227,7 @@
       <c r="F264" t="s">
         <v>9</v>
       </c>
-      <c r="G264" s="3" t="str">
+      <c r="G264" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55255,7 +55251,7 @@
       <c r="F265" t="s">
         <v>8</v>
       </c>
-      <c r="G265" s="3" t="str">
+      <c r="G265" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55279,7 +55275,7 @@
       <c r="F266" t="s">
         <v>11</v>
       </c>
-      <c r="G266" s="3" t="str">
+      <c r="G266" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55303,7 +55299,7 @@
       <c r="F267" t="s">
         <v>10</v>
       </c>
-      <c r="G267" s="3" t="str">
+      <c r="G267" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/10</v>
       </c>
@@ -55327,7 +55323,7 @@
       <c r="F268" t="s">
         <v>14</v>
       </c>
-      <c r="G268" s="3" t="str">
+      <c r="G268" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55351,7 +55347,7 @@
       <c r="F269" t="s">
         <v>9</v>
       </c>
-      <c r="G269" s="3" t="str">
+      <c r="G269" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55375,7 +55371,7 @@
       <c r="F270" t="s">
         <v>8</v>
       </c>
-      <c r="G270" s="3" t="str">
+      <c r="G270" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55399,7 +55395,7 @@
       <c r="F271" t="s">
         <v>9</v>
       </c>
-      <c r="G271" s="3" t="str">
+      <c r="G271" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55423,7 +55419,7 @@
       <c r="F272" t="s">
         <v>11</v>
       </c>
-      <c r="G272" s="3" t="str">
+      <c r="G272" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55447,7 +55443,7 @@
       <c r="F273" t="s">
         <v>13</v>
       </c>
-      <c r="G273" s="3" t="str">
+      <c r="G273" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55471,7 +55467,7 @@
       <c r="F274" t="s">
         <v>13</v>
       </c>
-      <c r="G274" s="3" t="str">
+      <c r="G274" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55495,7 +55491,7 @@
       <c r="F275" t="s">
         <v>11</v>
       </c>
-      <c r="G275" s="3" t="str">
+      <c r="G275" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55519,7 +55515,7 @@
       <c r="F276" t="s">
         <v>13</v>
       </c>
-      <c r="G276" s="3" t="str">
+      <c r="G276" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55543,7 +55539,7 @@
       <c r="F277" t="s">
         <v>8</v>
       </c>
-      <c r="G277" s="3" t="str">
+      <c r="G277" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55567,7 +55563,7 @@
       <c r="F278" t="s">
         <v>9</v>
       </c>
-      <c r="G278" s="3" t="str">
+      <c r="G278" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55591,7 +55587,7 @@
       <c r="F279" t="s">
         <v>10</v>
       </c>
-      <c r="G279" s="3" t="str">
+      <c r="G279" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55615,7 +55611,7 @@
       <c r="F280" t="s">
         <v>8</v>
       </c>
-      <c r="G280" s="3" t="str">
+      <c r="G280" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55639,7 +55635,7 @@
       <c r="F281" t="s">
         <v>8</v>
       </c>
-      <c r="G281" s="3" t="str">
+      <c r="G281" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55663,7 +55659,7 @@
       <c r="F282" t="s">
         <v>13</v>
       </c>
-      <c r="G282" s="3" t="str">
+      <c r="G282" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55687,7 +55683,7 @@
       <c r="F283" t="s">
         <v>11</v>
       </c>
-      <c r="G283" s="3" t="str">
+      <c r="G283" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55711,7 +55707,7 @@
       <c r="F284" t="s">
         <v>13</v>
       </c>
-      <c r="G284" s="3" t="str">
+      <c r="G284" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55735,7 +55731,7 @@
       <c r="F285" t="s">
         <v>8</v>
       </c>
-      <c r="G285" s="3" t="str">
+      <c r="G285" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55759,7 +55755,7 @@
       <c r="F286" t="s">
         <v>11</v>
       </c>
-      <c r="G286" s="3" t="str">
+      <c r="G286" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55783,7 +55779,7 @@
       <c r="F287" t="s">
         <v>8</v>
       </c>
-      <c r="G287" s="3" t="str">
+      <c r="G287" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55807,7 +55803,7 @@
       <c r="F288" t="s">
         <v>9</v>
       </c>
-      <c r="G288" s="3" t="str">
+      <c r="G288" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55831,7 +55827,7 @@
       <c r="F289" t="s">
         <v>13</v>
       </c>
-      <c r="G289" s="3" t="str">
+      <c r="G289" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55855,7 +55851,7 @@
       <c r="F290" t="s">
         <v>9</v>
       </c>
-      <c r="G290" s="3" t="str">
+      <c r="G290" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55879,7 +55875,7 @@
       <c r="F291" t="s">
         <v>14</v>
       </c>
-      <c r="G291" s="3" t="str">
+      <c r="G291" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55903,7 +55899,7 @@
       <c r="F292" t="s">
         <v>8</v>
       </c>
-      <c r="G292" s="3" t="str">
+      <c r="G292" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55927,7 +55923,7 @@
       <c r="F293" t="s">
         <v>14</v>
       </c>
-      <c r="G293" s="3" t="str">
+      <c r="G293" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55951,7 +55947,7 @@
       <c r="F294" t="s">
         <v>9</v>
       </c>
-      <c r="G294" s="3" t="str">
+      <c r="G294" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55975,7 +55971,7 @@
       <c r="F295" t="s">
         <v>11</v>
       </c>
-      <c r="G295" s="3" t="str">
+      <c r="G295" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -55999,7 +55995,7 @@
       <c r="F296" t="s">
         <v>10</v>
       </c>
-      <c r="G296" s="3" t="str">
+      <c r="G296" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56023,7 +56019,7 @@
       <c r="F297" t="s">
         <v>8</v>
       </c>
-      <c r="G297" s="3" t="str">
+      <c r="G297" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56047,7 +56043,7 @@
       <c r="F298" t="s">
         <v>13</v>
       </c>
-      <c r="G298" s="3" t="str">
+      <c r="G298" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56071,7 +56067,7 @@
       <c r="F299" t="s">
         <v>13</v>
       </c>
-      <c r="G299" s="3" t="str">
+      <c r="G299" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56095,7 +56091,7 @@
       <c r="F300" t="s">
         <v>11</v>
       </c>
-      <c r="G300" s="3" t="str">
+      <c r="G300" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56119,7 +56115,7 @@
       <c r="F301" t="s">
         <v>8</v>
       </c>
-      <c r="G301" s="3" t="str">
+      <c r="G301" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56143,7 +56139,7 @@
       <c r="F302" t="s">
         <v>8</v>
       </c>
-      <c r="G302" s="3" t="str">
+      <c r="G302" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/11</v>
       </c>
@@ -56167,7 +56163,7 @@
       <c r="F303" t="s">
         <v>8</v>
       </c>
-      <c r="G303" s="3" t="str">
+      <c r="G303" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56191,7 +56187,7 @@
       <c r="F304" t="s">
         <v>11</v>
       </c>
-      <c r="G304" s="3" t="str">
+      <c r="G304" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56215,7 +56211,7 @@
       <c r="F305" t="s">
         <v>8</v>
       </c>
-      <c r="G305" s="3" t="str">
+      <c r="G305" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56239,7 +56235,7 @@
       <c r="F306" t="s">
         <v>13</v>
       </c>
-      <c r="G306" s="3" t="str">
+      <c r="G306" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56263,7 +56259,7 @@
       <c r="F307" t="s">
         <v>11</v>
       </c>
-      <c r="G307" s="3" t="str">
+      <c r="G307" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56287,7 +56283,7 @@
       <c r="F308" t="s">
         <v>13</v>
       </c>
-      <c r="G308" s="3" t="str">
+      <c r="G308" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56311,7 +56307,7 @@
       <c r="F309" t="s">
         <v>11</v>
       </c>
-      <c r="G309" s="3" t="str">
+      <c r="G309" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56335,7 +56331,7 @@
       <c r="F310" t="s">
         <v>8</v>
       </c>
-      <c r="G310" s="3" t="str">
+      <c r="G310" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56359,7 +56355,7 @@
       <c r="F311" t="s">
         <v>11</v>
       </c>
-      <c r="G311" s="3" t="str">
+      <c r="G311" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56383,7 +56379,7 @@
       <c r="F312" t="s">
         <v>13</v>
       </c>
-      <c r="G312" s="3" t="str">
+      <c r="G312" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56407,7 +56403,7 @@
       <c r="F313" t="s">
         <v>10</v>
       </c>
-      <c r="G313" s="3" t="str">
+      <c r="G313" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56431,7 +56427,7 @@
       <c r="F314" t="s">
         <v>8</v>
       </c>
-      <c r="G314" s="3" t="str">
+      <c r="G314" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56455,7 +56451,7 @@
       <c r="F315" t="s">
         <v>8</v>
       </c>
-      <c r="G315" s="3" t="str">
+      <c r="G315" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56479,7 +56475,7 @@
       <c r="F316" t="s">
         <v>9</v>
       </c>
-      <c r="G316" s="3" t="str">
+      <c r="G316" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56498,12 +56494,12 @@
         <v>7</v>
       </c>
       <c r="E317" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F317" t="s">
         <v>13</v>
       </c>
-      <c r="G317" s="3" t="str">
+      <c r="G317" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56527,7 +56523,7 @@
       <c r="F318" t="s">
         <v>14</v>
       </c>
-      <c r="G318" s="3" t="str">
+      <c r="G318" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56551,7 +56547,7 @@
       <c r="F319" t="s">
         <v>11</v>
       </c>
-      <c r="G319" s="3" t="str">
+      <c r="G319" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56575,7 +56571,7 @@
       <c r="F320" t="s">
         <v>9</v>
       </c>
-      <c r="G320" s="3" t="str">
+      <c r="G320" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56599,7 +56595,7 @@
       <c r="F321" t="s">
         <v>9</v>
       </c>
-      <c r="G321" s="3" t="str">
+      <c r="G321" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56623,7 +56619,7 @@
       <c r="F322" t="s">
         <v>10</v>
       </c>
-      <c r="G322" s="3" t="str">
+      <c r="G322" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56647,7 +56643,7 @@
       <c r="F323" t="s">
         <v>11</v>
       </c>
-      <c r="G323" s="3" t="str">
+      <c r="G323" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56671,7 +56667,7 @@
       <c r="F324" t="s">
         <v>8</v>
       </c>
-      <c r="G324" s="3" t="str">
+      <c r="G324" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56690,12 +56686,12 @@
         <v>7</v>
       </c>
       <c r="E325" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F325" t="s">
         <v>13</v>
       </c>
-      <c r="G325" s="3" t="str">
+      <c r="G325" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56719,7 +56715,7 @@
       <c r="F326" t="s">
         <v>11</v>
       </c>
-      <c r="G326" s="3" t="str">
+      <c r="G326" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56743,7 +56739,7 @@
       <c r="F327" t="s">
         <v>9</v>
       </c>
-      <c r="G327" s="3" t="str">
+      <c r="G327" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56767,7 +56763,7 @@
       <c r="F328" t="s">
         <v>8</v>
       </c>
-      <c r="G328" s="3" t="str">
+      <c r="G328" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56791,7 +56787,7 @@
       <c r="F329" t="s">
         <v>9</v>
       </c>
-      <c r="G329" s="3" t="str">
+      <c r="G329" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56815,7 +56811,7 @@
       <c r="F330" t="s">
         <v>14</v>
       </c>
-      <c r="G330" s="3" t="str">
+      <c r="G330" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56839,7 +56835,7 @@
       <c r="F331" t="s">
         <v>9</v>
       </c>
-      <c r="G331" s="3" t="str">
+      <c r="G331" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56858,12 +56854,12 @@
         <v>7</v>
       </c>
       <c r="E332" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F332" t="s">
         <v>13</v>
       </c>
-      <c r="G332" s="3" t="str">
+      <c r="G332" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56887,7 +56883,7 @@
       <c r="F333" t="s">
         <v>11</v>
       </c>
-      <c r="G333" s="3" t="str">
+      <c r="G333" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56906,12 +56902,12 @@
         <v>7</v>
       </c>
       <c r="E334" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F334" t="s">
         <v>13</v>
       </c>
-      <c r="G334" s="3" t="str">
+      <c r="G334" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2025/12</v>
       </c>
@@ -56935,7 +56931,7 @@
       <c r="F335" t="s">
         <v>8</v>
       </c>
-      <c r="G335" s="3" t="str">
+      <c r="G335" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -56954,12 +56950,12 @@
         <v>7</v>
       </c>
       <c r="E336" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F336" t="s">
         <v>13</v>
       </c>
-      <c r="G336" s="3" t="str">
+      <c r="G336" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -56983,7 +56979,7 @@
       <c r="F337" t="s">
         <v>8</v>
       </c>
-      <c r="G337" s="3" t="str">
+      <c r="G337" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57002,12 +56998,12 @@
         <v>7</v>
       </c>
       <c r="E338" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F338" t="s">
         <v>8</v>
       </c>
-      <c r="G338" s="3" t="str">
+      <c r="G338" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57031,7 +57027,7 @@
       <c r="F339" t="s">
         <v>10</v>
       </c>
-      <c r="G339" s="3" t="str">
+      <c r="G339" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57055,7 +57051,7 @@
       <c r="F340" t="s">
         <v>11</v>
       </c>
-      <c r="G340" s="3" t="str">
+      <c r="G340" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57074,12 +57070,12 @@
         <v>7</v>
       </c>
       <c r="E341" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F341" t="s">
         <v>13</v>
       </c>
-      <c r="G341" s="3" t="str">
+      <c r="G341" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57103,7 +57099,7 @@
       <c r="F342" t="s">
         <v>9</v>
       </c>
-      <c r="G342" s="3" t="str">
+      <c r="G342" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57127,7 +57123,7 @@
       <c r="F343" t="s">
         <v>10</v>
       </c>
-      <c r="G343" s="3" t="str">
+      <c r="G343" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57151,7 +57147,7 @@
       <c r="F344" t="s">
         <v>14</v>
       </c>
-      <c r="G344" s="3" t="str">
+      <c r="G344" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57175,7 +57171,7 @@
       <c r="F345" t="s">
         <v>9</v>
       </c>
-      <c r="G345" s="3" t="str">
+      <c r="G345" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
@@ -57194,12 +57190,12 @@
         <v>7</v>
       </c>
       <c r="E346" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F346" t="s">
         <v>13</v>
       </c>
-      <c r="G346" s="3" t="str">
+      <c r="G346" t="str">
         <f>YEAR(Table13[[#This Row],[Hora de início]])&amp;"/"&amp;IF(MONTH(Table13[[#This Row],[Hora de início]])&lt;10,"0"&amp;MONTH(Table13[[#This Row],[Hora de início]]),MONTH(Table13[[#This Row],[Hora de início]]))</f>
         <v>2026/01</v>
       </c>
